--- a/skills/phd-advisor-outreach/assets/intent-table-template.xlsx
+++ b/skills/phd-advisor-outreach/assets/intent-table-template.xlsx
@@ -1120,8 +1120,8 @@
     <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="不在列表里" error="请从下拉列表里选" type="list">
       <formula1>"首选,重点,备选,保底,待定"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="不在列表里" error="请从下拉列表里选" type="list">
-      <formula1>"已加,未加,对方未提"</formula1>
+    <dataValidation sqref="F5:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"已加,已申请待通过,未加,对方未提"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1148,6 +1148,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1216,7 +1217,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>从下拉里选：已加、未加、对方未提</t>
+          <t>从下拉里选：已加、已申请待通过、未加、对方未提</t>
         </is>
       </c>
     </row>
@@ -1340,6 +1341,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1347,6 +1350,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -1355,7 +1359,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>导师回复欢迎报考，但没有说明名额或进一步安排</t>
+          <t>导师回复欢迎报考或说有名额，但还没有进一步的安排。名额的原话记在“名额情况”一列</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>导师表示可以聊一聊、加了微信，还没定时间</t>
+          <t>导师表示可以聊一聊、同意加微信或已经加上，还没定时间</t>
         </is>
       </c>
     </row>

--- a/skills/phd-advisor-outreach/assets/intent-table-template.xlsx
+++ b/skills/phd-advisor-outreach/assets/intent-table-template.xlsx
@@ -31,11 +31,11 @@
       <sz val="16"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,7 +54,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF243B53"/>
+        <fgColor rgb="00243B53"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,8 +67,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00D0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFD0D7DE"/>
+        <color rgb="00D0D7DE"/>
       </bottom>
     </border>
   </borders>
@@ -455,25 +464,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P34"/>
+  <dimension ref="A2:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -503,72 +503,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>意向状态</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>我的倾向</t>
+          <t>面试日期</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>名额情况</t>
+          <t>报名与考核时间</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>要定下来的节点</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>面试或交流日期</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>形式与要求</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>我的准备</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>报名时间</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>报名方式与材料</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>官方主页</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>下一步与提醒日期</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>最近更新</t>
         </is>
       </c>
     </row>
@@ -580,15 +535,6 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="4" t="n"/>
@@ -598,15 +544,6 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -616,15 +553,6 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="4" t="n"/>
@@ -634,15 +562,6 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="n"/>
@@ -652,15 +571,6 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="4" t="n"/>
@@ -670,15 +580,6 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="4" t="n"/>
@@ -688,15 +589,6 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="4" t="n"/>
@@ -706,15 +598,6 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="4" t="n"/>
@@ -724,15 +607,6 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="4" t="n"/>
@@ -742,15 +616,6 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -760,15 +625,6 @@
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="4" t="n"/>
@@ -778,15 +634,6 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="4" t="n"/>
@@ -796,15 +643,6 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="4" t="n"/>
@@ -814,15 +652,6 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="4" t="n"/>
@@ -832,15 +661,6 @@
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="4" t="n"/>
@@ -850,15 +670,6 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="4" t="n"/>
@@ -868,15 +679,6 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="4" t="n"/>
@@ -886,15 +688,6 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -904,15 +697,6 @@
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="4" t="n"/>
@@ -922,15 +706,6 @@
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="4" t="n"/>
@@ -940,15 +715,6 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="4" t="n"/>
@@ -958,15 +724,6 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4" t="n"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="4" t="n"/>
@@ -976,15 +733,6 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="n"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="4" t="n"/>
@@ -994,15 +742,6 @@
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="4" t="n"/>
@@ -1012,15 +751,6 @@
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="4" t="n"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="4" t="n"/>
@@ -1030,15 +760,6 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="4" t="n"/>
@@ -1048,15 +769,6 @@
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="4" t="n"/>
@@ -1066,15 +778,6 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="4" t="n"/>
@@ -1084,15 +787,6 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
-      <c r="O33" s="4" t="n"/>
-      <c r="P33" s="4" t="n"/>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="4" t="n"/>
@@ -1102,28 +796,8 @@
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="C5:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="不在列表里" error="请从下拉列表里选" type="list">
-      <formula1>"欢迎报考,愿意进一步交流,已约面试,面试后待反馈,明确接收意向,已报名,拟录取,暂无名额,暂不推进"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="不在列表里" error="请从下拉列表里选" type="list">
-      <formula1>"首选,重点,备选,保底,待定"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F5:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"已加,已申请待通过,未加,对方未提"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1134,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1148,7 +822,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1176,286 +849,103 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>意向状态</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>从下拉里选。按导师的原话判断，不往上加</t>
+          <t>用自己的话写一句现在什么情况就行，不用套固定的词。例如：“加了微信，等面试通知”“说有名额，还没约时间”“10/12 线上汇报已约”“面试完了等反馈”“有意向，但互为备选”“说考核通过愿意收”</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>我的倾向</t>
+          <t>面试日期</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>从下拉里选：首选、重点、备选、保底、待定</t>
+          <t>和这位老师约的交流或面试。定了写具体时间，没定写老师说的大概时间，如“10 月 7 日后”“名额确定后”</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>名额情况</t>
+          <t>报名与考核时间</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>导师关于名额的原话，如“今年有 1 个名额”“名额确定后通知”</t>
+          <t>学校这一关的日期：报名起止，综合考核或面试在哪几天。还没公布就写上一年的作参考，并注明“待公布”</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>要定下来的节点</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>从下拉里选：已加、已申请待通过、未加、对方未提</t>
+          <t>到了那天必须做选择的日子，写日期和原因，如“12/15 报名截止，同校只能填一位导师”“老师说名额留到月底”。没有就空着</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>面试或交流日期</t>
+          <t>下一步与提醒日期</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>具体到时间；没定就写导师说的大概时间，如“10 月 7 日后”</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>形式与要求</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>线上还是线下、用什么软件、PPT 讲多久、导师要求讲什么</t>
+          <t>接下来要做的一件事，以及最晚哪天做</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>我的准备</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PPT、导师文献精读、补课清单各到哪一步</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>这张表怎么用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>报名时间</t>
+          <t>谁来填</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>目标年份的报名起止时间；还没公布就写上一年的作参考，并注明“待公布”</t>
+          <t>主要由 AI 根据你说的情况来填和更新，你也可以自己改。你只需要告诉它现在什么情况</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>报名方式与材料</t>
+          <t>细节记在哪</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>报名系统、要交的材料、英语等硬门槛、推荐信要求</t>
+          <t>老师的原话、你对老师说过什么、每次往来，AI 记在“02_档案”的联系账本里；论文读到哪、要补什么，记在这位老师的文件夹和你的档案里。这张表只留一眼能看完的信息</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>两条底线</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>导师当前的研究方向，取自核查记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>官方主页</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>个人页或课题组主页</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>下一步与提醒日期</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>接下来要做的一件事，以及最晚哪天做</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>互为备选、导师提的特别要求、需要留意的事</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>最近更新</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>这一行最后一次改动的日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>意向状态的含义</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>欢迎报考</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>导师回复欢迎报考或说有名额，但还没有进一步的安排。名额的原话记在“名额情况”一列</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>愿意进一步交流</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>导师表示可以聊一聊、同意加微信或已经加上，还没定时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>已约面试</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>线上或线下交流的时间已经定了</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>面试后待反馈</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>已经交流过，等导师的答复</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>明确接收意向</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>导师明确表示愿意接收。仍需通过学院的考核，不等于录取</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>已报名</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>已在学校系统完成报名</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>拟录取</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>出现在学院的拟录取名单里</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>暂无名额</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>之前有意向，后来确认今年没有名额</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>暂不推进</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>自己决定不再推进</t>
+          <t>正式结果出来之前，至少留一个能同时走的备选；改主意可以，但要在节点之前告诉对方，不无声消失</t>
         </is>
       </c>
     </row>
